--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TestCases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestCases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TC001 - Flags ON: códigos de Reactivación (O, V, I, W) permiten el paso con tipoSolicitud 3</t>
+          <t>TC001 - Zona Gris sin campaña: el afiliado ve la pantalla "Un asesor continuará atendiendo tu solicitud"</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -530,14 +530,11 @@
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Precondiciones:
-- Flag Reactivación: true
-- Flag Incremento: true (cualquier valor)
-- Usuarios con códigos de Reactivación en bolsillo 31 y tarjetaAmparada: false
-  · CC 52526685 → código O (CUPO CONGELADO)
-  · CC 51760693 → código V (CUENTA DEVOLUCION VOLUNTARIA)
-  · CC 41336668 → código V (CUENTA DEVOLUCION VOLUNTARIA)
-  · CC 79528108 → código I (INACTIVO)
-  · Pendiente dato → código W</t>
+- Ambiente QA: https://dev.colsubsidio.com/creditos/solicitud/cupo-de-credito/onboarding
+- Cédula autorizada (CO1C) sin campaña, sin casos en curso, que en QA obtenga resultado Zona Gris del motor (dato pendiente de entregar)
+- Usuario del portal transaccional con clave conocida
+- Contenido de la pantalla de derivación publicado en Drupal (tarea 227151)
+- Referencia visual: Figma node 32745-131878 (pantalla 7.1)</t>
         </is>
       </c>
       <c r="F3" s="3" t="n"/>
@@ -548,7 +545,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Given que los usuarios anteriores inician solicitud de crédito con flag Reactivación activo</t>
+          <t>Given el afiliado inicia sesión, supera las validaciones, acepta las políticas y diligencia el Paso 1 (información personal)</t>
         </is>
       </c>
       <c r="F4" s="3" t="n"/>
@@ -559,7 +556,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>When se consume POST /loans/eligibility/internal/v1/card-validations para cada usuario con tipo CO1C</t>
+          <t>When el flujo ejecuta el motor de decisión en el Paso 2 (personalización de la solicitud) y el motor clasifica la solicitud como Zona Gris</t>
         </is>
       </c>
       <c r="F5" s="3" t="n"/>
@@ -570,12 +567,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Then la respuesta HTTP es 200 para todos</t>
+          <t>Then el front recibe la notificación de Bizagi con paso OFFER_RESULT y el estado de Zona Gris (hoy estadoPaso MANUAL, o el que se defina)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>Notificación OFFER_RESULT con el estado de Zona Gris</t>
         </is>
       </c>
     </row>
@@ -585,12 +582,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>And el campo estado es OK para todos</t>
+          <t>And se muestra la pantalla de derivación con título, texto, imagen del asesor y enlace</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>"estado": "OK"</t>
+          <t>Título: "Un asesor continuará atendiendo tu solicitud" / Texto: "Recibirás atención personalizada para indicarte los pasos a seguir. Si lo prefieres, puedes comunicarte al número celular [número configurado en Drupal]" / Enlace: "Ir a Colsubsidio.com"</t>
         </is>
       </c>
     </row>
@@ -600,12 +597,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>And el campo tipoSolicitud es 3 para todos (códigos O, V, I, W)</t>
+          <t>And la pantalla no muestra botón de regresar ni continúa a la pantalla de oferta ("¡Felicidades…!")</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>"tipoSolicitud": 3</t>
+          <t>Sin botón atrás; el flujo no avanza a la oferta</t>
         </is>
       </c>
     </row>
@@ -615,12 +612,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>And el campo tarjetaAmparada es false para todos</t>
+          <t>And al hacer clic en "Ir a Colsubsidio.com"</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>"tarjetaAmparada": false</t>
+          <t>Navega a https://www.colsubsidio.com</t>
         </is>
       </c>
     </row>
@@ -632,7 +629,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TC002 - Flags ON: códigos de Incremento (1, N, S) permiten el paso con tipoSolicitud 2</t>
+          <t>TC002 - Zona Gris con preaprobado: la solicitud se deriva al canal asistido</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -654,16 +651,9 @@
       <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Precondiciones:
-- Flag Reactivación: true (cualquier valor)
-- Flag Incremento: true
-- Usuarios con códigos de Incremento en bolsillo 31 y tarjetaAmparada: false
-  · CC 80810798   → código 1 (NORMAL)
-  · CC 1140814422 → código 1, tarjeta estado 7 (CAMBIO DE CLAVE OBLIGATORIO)
-  · CC 1097397286 → código 1, tarjeta estado S (SUSPENDIDO/SOBRECUPO)
-  · CC 52966724   → código 1, tarjeta estado 0 (PENDIENTE POR ACTIVAR)
-  · CC 1023876310 → código 1 (NORMAL)
-  · Pendiente dato → código N
-  · Pendiente dato → código S</t>
+- Ambiente QA
+- Cédula autorizada con campaña de preaprobado vigente que en QA obtenga Zona Gris (dato pendiente)
+- Fuente: HU 202180 (Caso 1.1: preaprobado que el motor manda a Zona Gris)</t>
         </is>
       </c>
       <c r="F11" s="3" t="n"/>
@@ -674,10 +664,14 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Given que los usuarios anteriores inician solicitud de crédito con flag Incremento activo</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n"/>
+          <t>Given el afiliado inicia sesión y en el Paso 1 visualiza el modal de preaprobado</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Modal de preaprobado visible</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="D13" s="3" t="n">
@@ -685,7 +679,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>When se consume POST /loans/eligibility/internal/v1/card-validations para cada usuario con tipo CO1C</t>
+          <t>When continúa el flujo y el motor de decisión clasifica la solicitud como Zona Gris</t>
         </is>
       </c>
       <c r="F13" s="3" t="n"/>
@@ -696,12 +690,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Then la respuesta HTTP es 200 para todos</t>
+          <t>Then se muestra la misma pantalla de derivación del TC001</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>"Un asesor continuará atendiendo tu solicitud" con el celular configurado en Drupal</t>
         </is>
       </c>
     </row>
@@ -711,739 +705,738 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>And el campo estado es OK para todos</t>
+          <t>And el flujo no continúa a la oferta del preaprobado</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>"estado": "OK"</t>
+          <t>No se muestra la pantalla de oferta</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="D16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>And el campo tipoSolicitud es 2 para todos (códigos 1, N, S)</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>"tipoSolicitud": 2</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>TC003 - Aprobado en firme: la solicitud NO se deriva (caso de control)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="D17" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>And el campo tarjetaAmparada es false para todos</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>"tarjetaAmparada": false</t>
-        </is>
-      </c>
+          <t>Precondiciones:
+- Ambiente QA
+- Cédula autorizada con campaña de aprobado en firme vigente
+- Fuente: HU 180005 (la compuerta posterior al motor envía la oferta en firme siempre por "Aprobado")
+- Confirmar que la misma compuerta aplica al autogestionado</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>TC003 - Flags OFF: códigos de Reactivación e Incremento son bloqueados</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Ecosistema Digital Crédito y Seguros</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
+      <c r="D18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Given el afiliado inicia sesión y en el Paso 1 visualiza el modal "¡Hola {nombre}, tienes un aprobado!"</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="D19" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Precondiciones:
-- Flag Reactivación: false
-- Flag Incremento: false
-- Usuarios con códigos de novedad
-  · CC 41336668 → código V (Reactivación)
-  · CC 79528108 → código I (Reactivación)
-  · CC 1140814422 → código 1 (Incremento)
-  · CC 80810798 → código 1 (Incremento)</t>
+          <t>When continúa el flujo y se ejecuta el motor de decisión</t>
         </is>
       </c>
       <c r="F19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="D20" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Given que los usuarios anteriores inician solicitud de crédito con ambas flags desactivadas</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n"/>
+          <t>Then el flujo continúa a la pantalla de oferta del Paso 2</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Pantalla "¡Felicidades {nombre}…!" con el cupo de la campaña</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="D21" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>When se consume POST /loans/eligibility/internal/v1/card-validations para cada usuario</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n"/>
+          <t>And no se muestra la pantalla de derivación al asesor</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>No aparece "Un asesor continuará atendiendo tu solicitud"</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="D22" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Then la respuesta HTTP es 200 para todos</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>TC004 - Regresión: el motor aprueba (OK) y el flujo continúa a la personalización de la oferta</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="D23" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>And el campo estado es VALIDATION_ERROR para todos</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>"estado": "VALIDATION_ERROR"</t>
-        </is>
-      </c>
+          <t>Precondiciones:
+- Ambiente QA
+- Cédula autorizada sin campaña que en QA obtenga resultado Aprobado</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="D24" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>And el campo tipoSolicitud NO está presente en ninguna respuesta</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>tipoSolicitud ausente</t>
-        </is>
-      </c>
+          <t>Given el afiliado completa validaciones, políticas y Paso 1</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="D25" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>And el campo codigoErrorValidacion es INVALID_REQUIREMENTS para todos</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>"codigoErrorValidacion": "INVALID_REQUIREMENTS"</t>
-        </is>
-      </c>
+          <t>When el motor de decisión responde Aprobado</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>TC004 - Flags independientes: cada flag bloquea solo su tipo de novedad</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Ecosistema Digital Crédito y Seguros</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Then el front recibe OFFER_RESULT con estadoPaso OK y muestra la pantalla de oferta</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Pantalla de oferta del Paso 2 sin cambios frente al comportamiento actual</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Precondiciones:
-- Escenario A: Flag Reactivación ON, Flag Incremento OFF
-  · CC 79528108 → código I (Reactivación) debe pasar
-  · CC 1140814422 → código 1 (Incremento) debe bloquearse
-- Escenario B: Flag Reactivación OFF, Flag Incremento ON
-  · CC 1140814422 → código 1 (Incremento) debe pasar
-  · CC 79528108 → código I (Reactivación) debe bloquearse</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n"/>
+          <t>And no se asigna estado de derivación ni se muestra la pantalla del asesor</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Sin derivación</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="D28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Given escenario A: Flag Reactivación ON, Flag Incremento OFF</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>TC005 - Regresión: el motor niega (FAIL) y se muestra la pantalla de negación</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="D29" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>When se consume el servicio con CC 79528108 (código I)</t>
+          <t>Precondiciones:
+- Ambiente QA
+- Cédula autorizada que en QA obtenga resultado Negado</t>
         </is>
       </c>
       <c r="F29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="D30" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Then el estado es OK y tipoSolicitud es 3</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>"estado": "OK", "tipoSolicitud": 3</t>
-        </is>
-      </c>
+          <t>Given el afiliado completa validaciones, políticas y Paso 1</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="D31" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>When se consume el servicio con CC 1140814422 (código 1)</t>
+          <t>When el motor de decisión responde Negado</t>
         </is>
       </c>
       <c r="F31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="D32" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Then el estado es VALIDATION_ERROR y tipoSolicitud ausente</t>
+          <t>Then el front recibe OFFER_RESULT con estadoPaso FAIL y muestra la pantalla de negación actual</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>"estado": "VALIDATION_ERROR", tipoSolicitud ausente</t>
+          <t>Pantalla de negación sin cambios</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Given escenario B: Flag Reactivación OFF, Flag Incremento ON</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n"/>
+          <t>And no se muestra la pantalla de derivación al asesor</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Sin derivación</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="D34" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>When se consume el servicio con CC 1140814422 (código 1)</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>TC006 - El afiliado derivado no puede continuar el flujo autogestionado mediante navegación</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="D35" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Then el estado es OK y tipoSolicitud es 2</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>"estado": "OK", "tipoSolicitud": 2</t>
-        </is>
-      </c>
+          <t>Precondiciones:
+- Afiliado en la pantalla de derivación (resultado del TC001)
+- Nota: la carga documental autogestionada no existe en 2026; se valida que no se pueda avanzar a ningún paso siguiente</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="D36" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>When se consume el servicio con CC 79528108 (código I)</t>
+          <t>Given el afiliado está en la pantalla "Un asesor continuará atendiendo tu solicitud"</t>
         </is>
       </c>
       <c r="F36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Then el estado es VALIDATION_ERROR y tipoSolicitud ausente</t>
+          <t>When usa el botón atrás y el botón adelante del navegador</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>"estado": "VALIDATION_ERROR", tipoSolicitud ausente</t>
+          <t>No regresa a pasos anteriores editables ni avanza a la oferta</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>TC005 - tarjetaAmparada bloquea siempre independiente del flag y código Ascard</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Ecosistema Digital Crédito y Seguros</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>And recarga la página (F5)</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Sigue viendo la pantalla de derivación o el mensaje transversal "Ya tienes una solicitud en curso con un asesor"</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Precondiciones:
-- Flag Reactivación: true
-- Flag Incremento: true
-- Usuarios con tarjetaAmparada: true (tienen tarjeta tipo 6)
-  · CC 52634111 → código I (Reactivación), tarjetaAmparada: true
-  · CC 1095915781 → código I (Reactivación), tarjetaAmparada: true
-  · CC 1013595547 → código I (Reactivación), tarjetaAmparada: true
-  · CC 20156603 → código I (Reactivación), tarjetaAmparada: true</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n"/>
+          <t>And escribe manualmente las URLs /cupo-de-credito/personalizacion-oferta, /datos-adicionales, /biometria y /fin</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>El middleware no permite continuar: termina en el mensaje transversal o en el login con requestState=CASE_IN_PROGRESS_PROMOTER</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="D40" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Given que los usuarios anteriores tienen tarjeta amparada tipo 6 e inician solicitud de crédito</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n"/>
+          <t>Then en ningún caso el afiliado llega a la oferta, la biometría o el fin de la solicitud</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Flujo autogestionado bloqueado</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="D41" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>When se consume POST /loans/eligibility/internal/v1/card-validations para cada usuario con tipo CO1C</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>TC007 - El texto y el celular de la pantalla de derivación provienen de Drupal</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="D42" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Then la respuesta HTTP es 200 para todos</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
+          <t>Precondiciones:
+- Contenido de la pantalla de derivación configurado en Drupal QA (tarea 227151)
+- Número de celular pendiente de definición por la PO (Edna Coca); se valida contra el valor configurado</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="D43" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>And el campo estado es VALIDATION_ERROR para todos aunque las flags estén activas</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>"estado": "VALIDATION_ERROR"</t>
-        </is>
-      </c>
+          <t>Given se consulta en Drupal QA el contenido configurado para la pantalla de derivación (título, texto, celular, imagen, enlace)</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="D44" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>And el campo tarjetaAmparada es true para todos</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>"tarjetaAmparada": true</t>
-        </is>
-      </c>
+          <t>When un afiliado es derivado a la pantalla del asesor</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="D45" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>And el campo tipoSolicitud NO está presente en ninguna respuesta</t>
+          <t>Then la pantalla muestra exactamente el título, texto, celular y enlace configurados en Drupal</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>tipoSolicitud ausente</t>
+          <t>Contenido idéntico a Drupal; ningún texto ni número quemado distinto al configurado</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>And el texto no contiene el placeholder "[canal de comunicación de preferencia]" (eliminado en el mockup final)</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Sin placeholders visibles</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>TC006 - Códigos Ascard desconocidos/mora bloquean siempre con ambas flags ON</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>TC008 - Un cambio del texto o del celular en Drupal se refleja sin desplegar código</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Ecosistema Digital Crédito y Seguros</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="D47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Precondiciones:
-- Flag Reactivación: true
-- Flag Incremento: true
-- Usuarios con códigos fuera de los sets de novedad
-  · CC 79584194 → código R (CUENTA REFINANCIADA)
-  · CC 19184974 → código K (CUENTA CASTIGADA)
-  · CC 19246507 → código J (CUENTA EN COBRO PRE JURIDICO)
-  · CC 11259747 → código J (CUENTA EN COBRO PRE JURIDICO)
-  · CC 547911   → código B (CUENTA CANCELADA POR EL BANCO)
-  · CC 1023944601 → código Y (COBRO JURIDICO)
-  · CC 13617086 → código A (POR MORA EN SUS PRODUCTOS)</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="D48" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Given que los usuarios anteriores inician solicitud de crédito</t>
+          <t>Precondiciones:
+- Acceso al administrador de Drupal QA (coordinar con David Avalos)
+- Valor original del texto y del celular registrado para revertirlo al terminar
+- Tiempo de caché aceptable definido con desarrollo</t>
         </is>
       </c>
       <c r="F48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="D49" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>When se consume POST /loans/eligibility/internal/v1/card-validations para cada usuario con tipo CO1C</t>
+          <t>Given se modifica en Drupal el texto informativo y el número celular de la pantalla de derivación y se publica</t>
         </is>
       </c>
       <c r="F49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="D50" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Then la respuesta HTTP es 200 para todos</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
+          <t>When, pasado el tiempo de caché acordado, un afiliado es derivado a la pantalla del asesor</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="D51" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>And el campo estado es VALIDATION_ERROR para todos</t>
+          <t>Then la pantalla muestra el texto y el celular nuevos</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>"estado": "VALIDATION_ERROR"</t>
+          <t>Cambios visibles sin despliegue de front</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="D52" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>And el campo tipoSolicitud NO está presente en ninguna respuesta</t>
+          <t>And se restaura el contenido original en Drupal</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>tipoSolicitud ausente</t>
+          <t>Contenido original restablecido</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="D53" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>And el campo codigoErrorValidacion es INVALID_REQUIREMENTS para todos</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>"codigoErrorValidacion": "INVALID_REQUIREMENTS"</t>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>TC009 - Con Drupal no disponible se muestra el texto de respaldo actualizado (no el mensaje anterior)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>TC007 - Sin tarjeta activa y tipo documento CE mapeado a CO1E</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Ecosistema Digital Crédito y Seguros</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
+      <c r="D54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Apoyo de desarrollo para dejar el contenido de Drupal no disponible en QA
+- Hoy el respaldo del código para MANUAL dice "Nuestro equipo analizará tu solicitud… recibirás respuesta en tu correo electrónico"</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="D55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Precondiciones:
-- Flag Reactivación: true
-- Flag Incremento: true
-- Escenario A: usuarios sin tarjeta multiservicios activa
-  · CC 80833648, CC 382429, CC 1024539415 → dataTarjeta vacío
-- Escenario B: usuario CE 382429
-  · El tipo CE debe enviarse como CO1E en el body (no como CE, genera HTTP 400)</t>
+          <t>Given Drupal no responde para el contenido de la pantalla de derivación</t>
         </is>
       </c>
       <c r="F55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="D56" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Given escenario A: usuarios sin tarjeta activa</t>
+          <t>When un afiliado es derivado a la pantalla del asesor</t>
         </is>
       </c>
       <c r="F56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="D57" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>When se consume POST /loans/eligibility/internal/v1/card-validations con tipo CO1C para CC 80833648, CC 382429, CC 1024539415</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="n"/>
+          <t>Then la pantalla muestra el contenido de respaldo sin quedar en blanco ni con errores</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Pantalla completa con contenido de respaldo</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="D58" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Then la respuesta HTTP es 200 para todos</t>
+          <t>And el contenido de respaldo corresponde al mensaje nuevo del asesor</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>No aparece "Nuestro equipo analizará tu solicitud… recibirás respuesta en tu correo electrónico"</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="D59" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>And el campo codigoErrorValidacion es CARD_STATUS</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>"codigoErrorValidacion": "CARD_STATUS"</t>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>TC010 - Versión móvil de la pantalla de derivación y del mensaje de reingreso</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="D60" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>And el campo reglaErrorValidacion es Tarjeta multiservicios no activa</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>"reglaErrorValidacion": "Tarjeta multiservicios no activa"</t>
-        </is>
-      </c>
+          <t>Precondiciones:
+- Dispositivo móvil o emulación móvil (ancho 375 px)
+- Referencia visual: Figma node 32750-132726</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="D61" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Given escenario B: usuario CE 382429</t>
+          <t>Given un afiliado es derivado a la pantalla del asesor desde un dispositivo móvil</t>
         </is>
       </c>
       <c r="F61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="D62" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>When se consume el servicio con body {"documento": {"tipo": "CO1E", "numero": "382429"}}</t>
+          <t>When se visualiza la pantalla</t>
         </is>
       </c>
       <c r="F62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="D63" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Then la respuesta HTTP es 200 (no 400 — el 400 ocurre si se envía tipo CE en lugar de CO1E)</t>
+          <t>Then textos, imagen y enlace se ven completos y alineados al mockup móvil, sin scroll horizontal</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>Pantalla 7.1 móvil conforme a Figma (las imágenes son de referencia)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="D64" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>And el campo codigoErrorValidacion es CARD_STATUS</t>
+          <t>And al reingresar desde el móvil, el mensaje transversal se ve conforme al mockup móvil</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>"codigoErrorValidacion": "CARD_STATUS"</t>
+          <t>Pantalla 7.2.2 móvil conforme a Figma</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1448,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>TC008 - Regresión: tipoSolicitud presente en OK, ausente en VALIDATION_ERROR</t>
+          <t>TC011 - E2E reingreso tras la derivación: se muestra "Ya tienes una solicitud en curso con un asesor"</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -1477,10 +1470,8 @@
       <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Precondiciones:
-- Flag Reactivación: true
-- Flag Incremento: true
-- Usuarios OK: CC 52526685 (Reactivación), CC 80810798 (Incremento)
-- Usuarios VALIDATION_ERROR: CC 19184974 (K), CC 79584194 (R), CC 52634111 (tarjetaAmparada)</t>
+- Misma cédula del TC001, ya derivada al canal asistido
+- Navegador cerrado después de la derivación</t>
         </is>
       </c>
       <c r="F66" s="3" t="n"/>
@@ -1491,7 +1482,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Given que se consumen usuarios que generan estado OK y usuarios que generan VALIDATION_ERROR</t>
+          <t>Given el afiliado abre la URL del Onboarding de Cupo y pulsa "Comenzar solicitud"</t>
         </is>
       </c>
       <c r="F67" s="3" t="n"/>
@@ -1502,7 +1493,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>When se revisan todas las respuestas OK</t>
+          <t>When inicia sesión en CIAM y el sistema valida el estado del caso (pantalla de carga)</t>
         </is>
       </c>
       <c r="F68" s="3" t="n"/>
@@ -1513,12 +1504,12 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Then el campo tipoSolicitud SIEMPRE está presente en respuestas con estado OK</t>
+          <t>Then el servicio de consulta de estado del caso (/request/check) responde estado CASE_IN_PROGRESS_PROMOTER</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>tipoSolicitud presente</t>
+          <t>"estado": "CASE_IN_PROGRESS_PROMOTER"</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1519,12 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>And tipoSolicitud es 3 para códigos de Reactivación (O, V, I, W)</t>
+          <t>And el front redirige a /login?requestState=CASE_IN_PROGRESS_PROMOTER y elimina la cookie userToken</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>"tipoSolicitud": 3</t>
+          <t>URL con requestState=CASE_IN_PROGRESS_PROMOTER; sin cookie userToken</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1534,12 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>And tipoSolicitud es 2 para códigos de Incremento (1, N, S)</t>
+          <t>And se muestra el mensaje transversal</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>"tipoSolicitud": 2</t>
+          <t>Título: "Ya tienes una solicitud en curso con un asesor" / Texto: "Si quieres retomar tu solicitud, comunícate con la Línea Audio Servicios (601) 7457900 Opción 2, para recibir orientación en los próximos pasos. Nuestro equipo estará disponible para ayudarte." / Botón "Conocer canales de servicio" / Enlace "Ir a Colsubsidio.com"</t>
         </is>
       </c>
     </row>
@@ -1558,38 +1549,980 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>When se revisan todas las respuestas VALIDATION_ERROR</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="n"/>
+          <t>And los textos ya no corresponden a la versión anterior</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>No aparece "…con un promotor" ni el botón "Conocer líneas de atención"</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="D73" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>Then el campo tipoSolicitud NUNCA está presente en respuestas con estado VALIDATION_ERROR</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>tipoSolicitud ausente en toda respuesta VALIDATION_ERROR</t>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>TC012 - Un caso derivado NO se retoma por el flujo digital</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="D74" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>And el campo datosError siempre está presente con codigoErrorValidacion y reglaErrorValidacion</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>datosError presente</t>
+          <t>Precondiciones:
+- Cédula con caso derivado al canal asistido
+- Riesgo a cubrir: un caso creado en autogestionado tiene operatorCode "01"; si la derivación no lo cambia, /request/check respondería IN_PROGRESS y el front haría retoma digital</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Given el afiliado con caso derivado inicia sesión nuevamente</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>When el sistema consulta el estado del caso en /request/check</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="D77" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Then la respuesta NO es estado IN_PROGRESS con pasoPendiente</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Estado distinto de IN_PROGRESS (esperado CASE_IN_PROGRESS_PROMOTER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="D78" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>And el front no redirige al paso pendiente (información personal, personalización de oferta, datos adicionales o biometría)</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>No hay retoma digital; se muestra el mensaje transversal del asesor</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>TC013 - Reingreso desde otro navegador o dispositivo con caso derivado</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="D80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Cédula con caso derivado al canal asistido
+- Navegador o dispositivo distinto al usado en la derivación, sin cookies previas</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="D81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Given el afiliado abre el Onboarding de Cupo desde el otro navegador o dispositivo</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>When inicia sesión</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Then se muestra el mensaje transversal "Ya tienes una solicitud en curso con un asesor"</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>El bloqueo depende del estado del caso en Bizagi, no de cookies del navegador anterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>TC014 - La derivación ocurre mientras el afiliado no está en la pantalla</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="D85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Cédula que en QA obtenga Zona Gris
+- Comportamiento esperado pendiente de confirmar con desarrollo (escenario no definido en la HU)</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Given el afiliado llega a la pantalla de carga del motor en el Paso 2</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>When cierra el navegador antes de recibir el resultado y el motor responde Zona Gris</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Then al volver a ingresar e iniciar sesión, ve el mensaje transversal del asesor</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>"Ya tienes una solicitud en curso con un asesor"</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="D89" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>And no es retomado a la personalización de la oferta</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Sin retoma digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>TC015 - Regresión: la retoma digital de un caso no derivado sigue funcionando</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="D91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Cédula autorizada con solicitud digital en curso NO derivada, abandonada en el Paso 1 o Paso 2</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Given el afiliado inicia sesión nuevamente</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="D93" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>When el sistema consulta el estado del caso en /request/check</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n"/>
+    </row>
+    <row r="94">
+      <c r="D94" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Then la respuesta es estado IN_PROGRESS con el pasoPendiente del caso</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>"estado": "IN_PROGRESS" + pasoPendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="D95" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>And el front lleva al afiliado al paso pendiente con sus datos (oferta y campaña si aplica)</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Retoma igual que antes del cambio; no se muestra el mensaje del asesor</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>TC016 - Regresión: un caso abierto por un asesor (no derivado) también muestra el mensaje transversal nuevo</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="D97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Cédula con caso en curso creado por un asesor en el canal asistido (operatorCode distinto de "01"), no proveniente de Zona Gris</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n"/>
+    </row>
+    <row r="98">
+      <c r="D98" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Given el afiliado intenta iniciar una solicitud en el autogestionado</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n"/>
+    </row>
+    <row r="99">
+      <c r="D99" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>When inicia sesión y el sistema valida el estado del caso</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="D100" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Then se muestra el mensaje transversal con el texto nuevo</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>"Ya tienes una solicitud en curso con un asesor" con la Línea Audio Servicios (601) 7457900 Opción 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="D101" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>And el botón "Conocer canales de servicio" navega a la URL definida</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>URL de destino del botón (pendiente de confirmar; hoy https://www.colsubsidio.com/consultanos/centros-de-servicio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>TC017 - Regresión condicional: la retoma de novedades (aumento/reactivación) no cambia</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="D103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Aplica solo si la tarea 227152 modifica /request/check
+- Cédula autorizada con novedad (aumento o reactivación) en curso, no derivada
+- Flags de retoma según HU 207400</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="D104" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Given el afiliado con la novedad en curso inicia sesión nuevamente</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="D105" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>When el sistema consulta el estado del caso</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Then la retoma de la novedad se comporta igual que antes del cambio</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Retoma según la matriz de flags de la HU 207400; sin mensaje del asesor</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>TC018 - [Pendiente definición] El caso derivado queda en la bandeja del asistido con estado temporal y trazabilidad</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="D108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Caso derivado por Zona Gris (TC001)
+- Acceso a Bizagi QA (bizagi_consultar_caso.py) o apoyo de Gattaca
+- Pendiente: nombre del estado temporal y actividad o cola destino (¿"Ofrecer Zona Gris", HU 203293?)</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Given se consulta en Bizagi el caso del afiliado derivado</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n"/>
+    </row>
+    <row r="110">
+      <c r="D110" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>When se revisa el estado, la actividad actual y el historial del caso</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="n"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Then el caso está en la actividad o cola definida para el canal asistido</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>Caso disponible para gestión del asesor</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="D112" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>And tiene el estado temporal definido, la fecha y hora del cambio de estado y el mismo idCaso original</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>Estado temporal + fecha/hora + idCaso sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="D113" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>And el canal de origen del caso es el autogestionado</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>canalOrigen: WEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="D114" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>And existe un único caso para el afiliado, también después del reingreso del TC011</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Sin casos duplicados</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>TC019 - [Pendiente definición] Las solicitudes derivadas se identifican en el reporte operativo</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="D116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Pendiente: nombre del reporte operativo y forma de acceso
+- Al menos una solicitud derivada por Zona Gris, una finalizada, una negada y una en trámite autogestionado</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Given se consulta el reporte operativo del periodo de las pruebas</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>When se filtran las solicitudes de las cédulas de prueba</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Then las solicitudes derivadas se muestran con el estado temporal definido</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Estado temporal visible en el reporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="D120" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>And se diferencian de las finalizadas, negadas y en trámite por el autogestionado</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Clasificación diferenciada</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>TC020 - [Pendiente definición] Falla al derivar la solicitud al canal asistido</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="D122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Apoyo de desarrollo o Gattaca para provocar la falla (la derivación ocurre dentro de Bizagi, no hay un endpoint aislado que tumbar)
+- Pendiente: qué pantalla ve el afiliado cuando la derivación falla</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Given el motor clasifica una solicitud como Zona Gris</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>When ocurre una falla o timeout al registrar el estado o enrutar el caso al asistido</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n"/>
+    </row>
+    <row r="125">
+      <c r="D125" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Then el afiliado ve la pantalla de error definida y no una pantalla en blanco ni un loader infinito</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>Pantalla de error definida (p. ej. EXECUTION_ERROR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="D126" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>And el caso conserva su estado y su información</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>Sin pérdida de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="D127" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>And no se crea un caso duplicado en el canal asistido</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>Un único caso</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>TC021 - [Pendiente definición] Reproceso de una derivación fallida</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="D129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Solicitud con falla en la derivación (TC020)
+- Pendiente: mecanismo de reproceso (automático o manual); la HU no lo define</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Given el servicio del canal asistido está restablecido</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="n"/>
+    </row>
+    <row r="131">
+      <c r="D131" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>When se ejecuta el mecanismo de reproceso definido</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Then la solicitud queda en la bandeja del asistido con el estado temporal</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Derivación completada</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="D133" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>And existe un único caso en la cola del asesor</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Sin duplicados</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>TC022 - [Pendiente alcance] Novedad (aumento o reactivación) clasificada como Zona Gris</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Ecosistema Digital Crédito y Seguros</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="D135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Precondiciones:
+- Pendiente: confirmar si la HU aplica a novedades
+- Cédula autorizada con novedad (aumento o reactivación) que en QA obtenga Zona Gris</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="n"/>
+    </row>
+    <row r="136">
+      <c r="D136" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Given el afiliado inicia una novedad por el autogestionado</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="n"/>
+    </row>
+    <row r="137">
+      <c r="D137" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>When el motor de decisión clasifica la solicitud como Zona Gris</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Then el comportamiento corresponde a la definición de alcance</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>Si aplica: pantalla de derivación (TC001). Si no aplica: comportamiento actual sin cambios</t>
         </is>
       </c>
     </row>
